--- a/employee_surveys/049_employee_training_platform_usability_evaluation_form--employee_surveys.xlsx
+++ b/employee_surveys/049_employee_training_platform_usability_evaluation_form--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'improve_training_content'}</t>
+          <t>improve_training_content</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Improve training content'}</t>
+          <t>Improve training content</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'simplify_training_process'}</t>
+          <t>simplify_training_process</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Simplify training process'}</t>
+          <t>Simplify training process</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'presentation'}</t>
+          <t>presentation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Presentation'}</t>
+          <t>Presentation</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'interactive'}</t>
+          <t>interactive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Interactive'}</t>
+          <t>Interactive</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'clear_navigation'}</t>
+          <t>clear_navigation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Clear navigation'}</t>
+          <t>Clear navigation</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'easy_search'}</t>
+          <t>easy_search</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Easy search'}</t>
+          <t>Easy search</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Not satisfied'}</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'recommend'}</t>
+          <t>recommend</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Recommend'}</t>
+          <t>Recommend</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'somewhat_recommend'}</t>
+          <t>somewhat_recommend</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Somewhat Recommend'}</t>
+          <t>Somewhat Recommend</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'not_recommend'}</t>
+          <t>not_recommend</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Not Recommend'}</t>
+          <t>Not Recommend</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'recommend'}</t>
+          <t>recommend</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Recommend'}</t>
+          <t>Recommend</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'somewhat_recommend'}</t>
+          <t>somewhat_recommend</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Somewhat Recommend'}</t>
+          <t>Somewhat Recommend</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'not_recommend'}</t>
+          <t>not_recommend</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Not Recommend'}</t>
+          <t>Not Recommend</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'easy'}</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Easy'}</t>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'difficult'}</t>
+          <t>difficult</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Difficult'}</t>
+          <t>Difficult</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'very_difficult'}</t>
+          <t>very_difficult</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Very difficult'}</t>
+          <t>Very difficult</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Not satisfied'}</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
